--- a/notebook/final files/output/pz_nefro_example_mapped.xlsx
+++ b/notebook/final files/output/pz_nefro_example_mapped.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\SCUOLA\3.RICERCA\1. Fellowship\UNIBO\Fellowship\Pharmacovigilance\Tacrolemia\Standardizzazione dati\dati\final files\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\SCUOLA\3.RICERCA\1. Fellowship\UNIBO\Fellowship\Pharmacovigilance\Std_dati_nefrologia\notebook\final files\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA95B74D-ABC4-461F-9094-42862801F55B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8411978-F290-4CDE-A13F-4EB742A3F173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="10245" windowHeight="10920" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GENERALE" sheetId="1" r:id="rId1"/>
@@ -1412,7 +1412,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1476,6 +1476,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDA269E"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1618,7 +1624,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1686,6 +1692,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4252,80 +4259,80 @@
         <v>189</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8">
+    <row r="8" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="25">
         <v>2</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="25" t="s">
         <v>190</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="25" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9">
+    <row r="9" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="25">
         <v>2</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="25" t="s">
         <v>190</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="25" t="s">
         <v>193</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="25" t="s">
         <v>182</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="25" t="s">
         <v>183</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="25" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10">
+    <row r="10" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="25">
         <v>2</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="25" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11">
+    <row r="11" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="25">
         <v>2</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="25" t="s">
         <v>194</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="25" t="s">
         <v>188</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="25" t="s">
         <v>189</v>
       </c>
     </row>
